--- a/route/Blue-Yellow Buses (Private)/77a.xlsx
+++ b/route/Blue-Yellow Buses (Private)/77a.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\arpan\Desktop\testing_gps_wifi_esp8266\Blue-Yellow Buses (Private)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\arpan\Desktop\NEXBUS_LIVE\route\Blue-Yellow Buses (Private)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{961EC697-D4EF-4A4F-9D04-18ADECB2C578}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00086EBC-98E3-4851-BB56-CD93490C59B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11160" xr2:uid="{0B9BFC91-FDC8-4C32-A803-B2924E15BD7A}"/>
+    <workbookView xWindow="10200" yWindow="0" windowWidth="10200" windowHeight="10920" xr2:uid="{0B9BFC91-FDC8-4C32-A803-B2924E15BD7A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -182,9 +182,6 @@
     <t>Brace Bridge(22°30'59.6"N 88°18'12.0"E)</t>
   </si>
   <si>
-    <t>Santoshpur (Down)(22°30'47.6"N 88°16'17.7"E)</t>
-  </si>
-  <si>
     <t>Taratala State Garage(22°30'57.1"N 88°18'23.6"E)</t>
   </si>
   <si>
@@ -261,6 +258,9 @@
   </si>
   <si>
     <t>Batanagar River Side(Down)(22°30'35.4"N 88°13'03.5"E)</t>
+  </si>
+  <si>
+    <t>Santoshpur (Down)(22°30'45.9"N 88°16'07.4"E)</t>
   </si>
 </sst>
 </file>
@@ -870,111 +870,111 @@
         <v>46</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>47</v>
+        <v>73</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B25" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B26" s="3" t="s">
         <v>50</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B27" s="3" t="s">
         <v>52</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B28" s="3" t="s">
         <v>54</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B29" s="3" t="s">
         <v>56</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B30" s="3" t="s">
         <v>58</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B31" s="3" t="s">
         <v>60</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B32" s="3" t="s">
         <v>62</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B33" s="3" t="s">
         <v>64</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B34" s="3" t="s">
         <v>66</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B35" s="3" t="s">
         <v>68</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B36" s="3" t="s">
         <v>70</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B37" s="3" t="s">
         <v>72</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
